--- a/excel/equipment.xlsx
+++ b/excel/equipment.xlsx
@@ -84,7 +84,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
-    <t>编号【KEY】</t>
+    <t>编号</t>
   </si>
   <si>
     <t>物品id</t>
@@ -1221,7 +1221,7 @@
     </row>
     <row r="4" s="1" customFormat="1" spans="1:16">
       <c r="A4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" s="3">
         <v>100001</v>
@@ -1249,7 +1249,7 @@
     </row>
     <row r="5" s="1" customFormat="1" spans="1:16">
       <c r="A5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="3">
         <v>100002</v>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="1:16">
       <c r="A6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="3">
         <v>100003</v>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="7" s="1" customFormat="1" spans="1:16">
       <c r="A7" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="3">
         <v>100004</v>
@@ -1333,7 +1333,7 @@
     </row>
     <row r="8" s="1" customFormat="1" spans="1:16">
       <c r="A8" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="3">
         <v>100005</v>
@@ -1361,7 +1361,7 @@
     </row>
     <row r="9" s="1" customFormat="1" spans="1:16">
       <c r="A9" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="3">
         <v>100006</v>
